--- a/reports/excel/plants/low_psh_plants_report_22-05-2026.xlsx
+++ b/reports/excel/plants/low_psh_plants_report_22-05-2026.xlsx
@@ -49,12 +49,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E44545"/>
+        <fgColor rgb="0041BA41"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0041BA41"/>
+        <fgColor rgb="00E44545"/>
       </patternFill>
     </fill>
     <fill>
@@ -486,9 +486,9 @@
     <col width="17" customWidth="1" min="10" max="10"/>
     <col width="6" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="17" customWidth="1" min="17" max="17"/>
     <col width="22" customWidth="1" min="18" max="18"/>
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>FAULTY</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -622,32 +622,32 @@
         <v>770.66</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>79.78</v>
+        <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.19</v>
+        <v>3.53</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>149.47</v>
+        <v>2723.18</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>3472.63</v>
+        <v>6046.34</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.19</v>
+        <v>3.53</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0.19</v>
+        <v>3.53</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.171</v>
+        <v>3.177</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>UNDERPERFORMING</t>
+          <t>NO COMPARISON REQUIRED</t>
         </is>
       </c>
       <c r="P2" s="2" t="n">
@@ -655,14 +655,14 @@
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="R2" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S2" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1">
@@ -673,7 +673,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>FAULTY</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -695,47 +695,47 @@
         <v>240.56</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>126.04</v>
+        <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.62</v>
+        <v>5.29</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>149.49</v>
+        <v>1273.34</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>18010.43</v>
+        <v>19134.28</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.62</v>
+        <v>5.29</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>4</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0.485</v>
+        <v>3.805</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.4365</v>
+        <v>3.4245</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>UNDERPERFORMING</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="P3" s="2" t="n">
-        <v>27.84</v>
+        <v>39.03</v>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="R3" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S3" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
@@ -744,7 +744,7 @@
           <t>MAJOR ENGINEERING LOT 10</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
@@ -768,47 +768,47 @@
         <v>71.92</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>26.53</v>
+        <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.47</v>
+        <v>3.53</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>33.48</v>
+        <v>253.66</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>5753.11</v>
+        <v>5973.29</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.47</v>
+        <v>3.53</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>4</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.485</v>
+        <v>3.805</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.4365</v>
+        <v>3.4245</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>UNDERPERFORMING</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="P4" s="2" t="n">
-        <v>-3.09</v>
+        <v>-7.23</v>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="R4" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S4" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
@@ -817,9 +817,9 @@
           <t>MAJOR ENGINEERING LOT 8</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>OFFLINE</t>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -844,25 +844,25 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.19</v>
+        <v>1.44</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>9.94</v>
+        <v>75.17</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1277.08</v>
+        <v>1342.31</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.19</v>
+        <v>1.44</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.485</v>
+        <v>3.805</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.4365</v>
+        <v>3.4245</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="P5" s="2" t="n">
-        <v>-60.82</v>
+        <v>-62.16</v>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
           <t>VINDA PHASE 4 (MSB 3-2)</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>FAULTY</t>
         </is>
@@ -914,47 +914,47 @@
         <v>2119.14</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1137.49</v>
+        <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.66</v>
+        <v>4.96</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1390.9</v>
+        <v>10519.37</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>580847.67</v>
+        <v>589976.14</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.66</v>
+        <v>4.96</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>4</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0.485</v>
+        <v>3.805</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.4365</v>
+        <v>3.4245</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>UNDERPERFORMING</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="P6" s="2" t="n">
-        <v>36.08</v>
+        <v>30.35</v>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="R6" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S6" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
@@ -1036,7 +1036,7 @@
           <t>IOI MALL PUCHONG (NEW WING) PHASE 2</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
@@ -1060,32 +1060,32 @@
         <v>2383.28</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>979.51</v>
+        <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.47</v>
+        <v>3.65</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1116.79</v>
+        <v>8703.16</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>347460.55</v>
+        <v>355046.92</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.47</v>
+        <v>3.65</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>0.47</v>
+        <v>3.65</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.423</v>
+        <v>3.285</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>UNDERPERFORMING</t>
+          <t>NO COMPARISON REQUIRED</t>
         </is>
       </c>
       <c r="P8" s="2" t="n">
@@ -1093,14 +1093,14 @@
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="R8" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S8" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
@@ -1151,10 +1151,10 @@
         <v>2</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0.235</v>
+        <v>1.87</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.2115</v>
+        <v>1.683</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
           <t>THOR SPECIALTIES</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
@@ -1206,32 +1206,32 @@
         <v>91.14</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>32.81</v>
+        <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.47</v>
+        <v>3.74</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>42.67</v>
+        <v>340.53</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>5626.14</v>
+        <v>5924</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.47</v>
+        <v>3.74</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>2</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>0.235</v>
+        <v>1.87</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.2115</v>
+        <v>1.683</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>UNDERPERFORMING</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="P10" s="2" t="n">
@@ -1239,14 +1239,14 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="R10" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S10" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
